--- a/receipts/American_Select_Expenses.xlsx
+++ b/receipts/American_Select_Expenses.xlsx
@@ -676,12 +676,14 @@
     <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3591,7 +3593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
         <v>133</v>
       </c>
@@ -3623,35 +3625,35 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" ht="42" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B83" s="12">
+    <row r="83" ht="42" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="12">
         <v>46150</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="B83" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D83" s="13" t="s">
+      <c r="C83" s="14" t="s">
         <v>135</v>
       </c>
+      <c r="D83" s="14">
+        <v>223.98</v>
+      </c>
       <c r="E83" s="14">
-        <v>223.98</v>
+        <v>0</v>
       </c>
       <c r="F83" s="14">
-        <v>0</v>
+        <v>15.68</v>
       </c>
       <c r="G83" s="14">
-        <v>15.68</v>
+        <v>0</v>
       </c>
       <c r="H83" s="15">
-        <v>0</v>
-      </c>
-      <c r="I83" s="16">
         <v>239.66</v>
       </c>
-      <c r="J83" s="4" t="s">
+      <c r="I83" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="K83">
+      <c r="J83" s="4">
         <v>2</v>
       </c>
     </row>
@@ -3666,19 +3668,19 @@
         <v>13</v>
       </c>
       <c r="D84" s="17">
-        <v>4759.67</v>
+        <v>4983.65</v>
       </c>
       <c r="E84" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F84" s="17">
-        <v>263.37</v>
+        <v>279.05</v>
       </c>
       <c r="G84" s="17">
         <v>3227.24</v>
       </c>
       <c r="H84" s="17">
-        <v>5243.41</v>
+        <v>5483.07</v>
       </c>
     </row>
   </sheetData>

--- a/receipts/American_Select_Expenses.xlsx
+++ b/receipts/American_Select_Expenses.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A232F38-1DE0-4C14-B8AE-49C66AA9CEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11175"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Expenses" state="visible" r:id="rId4"/>
+    <sheet name="Expenses" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -67,7 +73,7 @@
     <t>Rivoli Parfums</t>
   </si>
   <si>
-    <t xml:space="preserve">Eau de Vivre (M) Eau de Parfum 100 ml Spray | ×1 @ $14.99/unit
+    <t>Eau de Vivre (M) Eau de Parfum 100 ml Spray | ×1 @ $14.99/unit
 Harmonie de Jour (L) Eau de Parfum 120 ml Spray | ×1 @ $14.99/unit
 Reverie Pour Homme (M) Eau de Parfum 100 ml Spray | default $14.99 1 $14.99 ×1 @ $14.99/unit
 Blue Intense (M) Eau de Parfum 100 ml Spray | ×1 @ $14.99/unit
@@ -79,7 +85,7 @@
     <t>Daspar</t>
   </si>
   <si>
-    <t xml:space="preserve">LAZELL SPRING FOR WOMEN EDP 3.4 OZ 100 ML Perfume 590717658314 4 $5.85 3 $17.55 ×3 @ $5.85/unit
+    <t>LAZELL SPRING FOR WOMEN EDP 3.4 OZ 100 ML Perfume 590717658314 4 $5.85 3 $17.55 ×3 @ $5.85/unit
 TAJ MAX EXOTIC BLISS 3.4 OZ Dubai Long-Lasting Perfume $8.75 4 $̶3̶5̶.̶0̶0̶ $31.50 LAZELL BLACK ONYX WOMEN EDP 3.4 OZ NEW Perfume LZ-45 590781462618 9 $5.85 3 $17.55 ×3 @ $5.85/unit
 DASPAR DE HOMME MEN PERFUME WITH PHEROMONES 2.02 OZ 2452 $5.25 4 $̶2̶1̶.̶0̶0̶ $19.95 TAJ MAX AQUA SPORT 3.4 OZ Dubai Long-Lasting Perfume $8.75 3 $̶2̶6̶.̶2̶5̶ $23.63 LAZELL NIGHT BLOOM FOR WOMEN EDP 3.4 OZ 100 ML Perfume 590781462626 4 $3.15 6 $18.90 ×6 @ $3.15/unit</t>
   </si>
@@ -96,7 +102,7 @@
     <t>2026-01-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Miss COCO 3.4 oz EDP for Women – Gourmand ×6 @ $2.95/unit
+    <t>Miss COCO 3.4 oz EDP for Women – Gourmand ×6 @ $2.95/unit
 Infinity 3.3 oz EDT for Men – Fresh Fougere ×6 @ $2.95/unit
 Victory 3.3 oz EDT for Men – Fresh Amber Inspired Scent ×3 @ $2.95/unit
 Platinum 3.4 oz EDP for Men by Fragrance Couture – Chrome ×6 @ $3.15/unit
@@ -122,7 +128,7 @@
     <t>MYS Wholesale Inc</t>
   </si>
   <si>
-    <t xml:space="preserve">Prism Water Pray Cologne Eau De Toilette For Men - #02884-F ×3 @ $3.75/unit
+    <t>Prism Water Pray Cologne Eau De Toilette For Men - #02884-F ×3 @ $3.75/unit
 365 Day Spray Perfume Eau de Parfum For Women - #EBC1042-3 ×3 @ $4.00/unit
 Invincible Platinum Spray Cologne Eau De Toilette For Men ×3 @ $3.75/unit
 Adventure Club Perfume for Men ×3 @ $6.00/unit
@@ -148,7 +154,7 @@
     <t>Funteze</t>
   </si>
   <si>
-    <t xml:space="preserve">SEXY ROSE PINK SPRAY PERFUME EAU DE PARFUM | Pink / ONE SIZE(1) - #FTZEBC1059-3 ×3 @ $5.95/unit
+    <t>SEXY ROSE PINK SPRAY PERFUME EAU DE PARFUM | Pink / ONE SIZE(1) - #FTZEBC1059-3 ×3 @ $5.95/unit
 LOVE IS FOREVER SPRAY PERFUME EAU DE PARFUM | BLUSH / ONE SIZE(1) - #FTZEBC1369-3 ×3 @ $5.95/unit
 HONEY BEAR PINK SPRAY PERFUME EAU DE PARFUM | Pink / ONE SIZE(1) - #FTZFL3172 ×3 @ $5.95/unit
 NICE GIRL SPRAY PERFUME EAU DE PARFUM FOR WOMEN | PINK / ONE SIZE(1) - #FTZFL2922 ×3 @ $5.95/unit
@@ -184,7 +190,7 @@
     <t>2026-03-11</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr Teal's Eucalyptus &amp; Spearmint Body Lotion, 18 fl oz. ×3 @ $5.87/unit
+    <t>Dr Teal's Eucalyptus &amp; Spearmint Body Lotion, 18 fl oz. ×3 @ $5.87/unit
 Dr Teal's Restorative Minerals Body Lotion with Magnesium, Potassium &amp; Zinc, 18 oz ×3 @ $5.87/unit
 Dr Teal's 24 Hour Moisture Body Lotion with Lavender Essential Oil, 18 fl oz ×3 @ $5.87/unit
 Dr Teal's Body Wash with Pure Epsom Salt, Soothe &amp; Sleep with Lavender, 24 fl oz ×3 @ $5.87/unit
@@ -213,7 +219,7 @@
     <t>Lovery</t>
   </si>
   <si>
-    <t xml:space="preserve">LoveryBlack Affinity At Midnight Pheromone Perfume – 50ml ×1 @ $21.99/unit
+    <t>LoveryBlack Affinity At Midnight Pheromone Perfume – 50ml ×1 @ $21.99/unit
 Mens Cologne BROSS 3.4oz Eau De Parfum Spray, Masculine Mist ×1 @ $11.99/unit
 LoveryBlack Affinity For Him Pheromone Cologne – 50ml Cologn ×1 @ $21.99/unit
 Men’s Extreme 3.4oz Eau De Parfum - Men Perfume Spray ×1 @ $13.99/unit
@@ -281,7 +287,7 @@
     <t>Portable Power Bank with a Capacity of 10000/2… ×5 @ $4.98/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Valentine's Day Gift - New Smartwatch, Unisex G… ×1 @ $8.03/unit
+    <t>Valentine's Day Gift - New Smartwatch, Unisex G… ×1 @ $8.03/unit
 Valentine's Day Gift - New Smartwatch, Unisex G… ×1 @ $13.54/unit</t>
   </si>
   <si>
@@ -297,11 +303,11 @@
     <t>20000mAh large-capacity mobile power bank, … ×5 @ $5.27/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Nokia Go Earbuds+ TWS-201 ×5 @ $10.60/unit
+    <t>Nokia Go Earbuds+ TWS-201 ×5 @ $10.60/unit
 Nokia Go Earbuds+ TWS-201 ×4 @ $10.60/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Hyundai LP5 In-Ear Earphones Low-Accent Surr… ×5 @ $16.58/unit
+    <t>Hyundai LP5 In-Ear Earphones Low-Accent Surr… ×5 @ $16.58/unit
 Hyundai LP5 In-Ear Earphones Low-Accent Surr… ×5 @ $16.58/unit
 USB to Type-C Charging Cables in 12-Pack/15-P… ×1 @ $12.32/unit
 Set of 10 Cables, Each 6.6 Feet Long, Designed f… ×1 @ $11.37/unit</t>
@@ -319,11 +325,11 @@
     <t>20000mAh Large Capacity Mobile Power Supply,… ×5 @ $5.28/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5-Inch Full Screen Touch Sports Smartwatch Fe… ×1 @ $10.82/unit
+    <t>1.5-Inch Full Screen Touch Sports Smartwatch Fe… ×1 @ $10.82/unit
 1.5-Inch Full Screen Touch Sports Smartwatch Fe… ×1 @ $10.82/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5-Inch Full Screen Touch Sports Smartwatch Fe… ×1 @ $9.68/unit
+    <t>1.5-Inch Full Screen Touch Sports Smartwatch Fe… ×1 @ $9.68/unit
 1.5-Inch Full Screen Touch Sports Smartwatch Fe… ×1 @ $9.68/unit
 1.5-Inch Full Screen Touch Sports Smartwatch Fe… ×2 @ $10.79/unit</t>
   </si>
@@ -331,7 +337,7 @@
     <t>2025 New Smart Watch, 1.83-inch Touch Screen,… ×2 @ $4.99/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Reusable Stretchable Storage Lids for Round Pot… ×15 @ $2.10/unit
+    <t>Reusable Stretchable Storage Lids for Round Pot… ×15 @ $2.10/unit
 1000pcs Long Strip Perfume Test Strips - Dispos… ×1 @ $10.34/unit
 1000pcs of Elastic Food Wrap Covers, Food-Gra… ×1 @ $2.99/unit
 1000pcs of Elastic Food Wrap Covers, Food-Gra… ×5 @ $3.68/unit</t>
@@ -352,7 +358,7 @@
     <t>A 8.45oz RZSYZH USB Rechargeable Electric Ble… ×6 @ $5.96/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">12.85 Oz Rechargeable Portable Blender Cup, El… ×1 @ $4.12/unit
+    <t>12.85 Oz Rechargeable Portable Blender Cup, El… ×1 @ $4.12/unit
 12.85 Oz Rechargeable Portable Blender Cup, El… ×1 @ $4.12/unit
 12.85 Oz Rechargeable Portable Blender Cup, El… ×1 @ $4.12/unit
 12.85 Oz Rechargeable Portable Blender Cup, El… ×1 @ $4.12/unit
@@ -371,7 +377,7 @@
     <t>Portable Wireless Speaker, Small Wireless Speak… ×1 @ $5.40/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">TG192 A Large Capacity 2400mAh Outdoor Wire… ×1 @ $12.86/unit
+    <t>TG192 A Large Capacity 2400mAh Outdoor Wire… ×1 @ $12.86/unit
 TG192 A Large Capacity 2400mAh Outdoor Wire… ×1 @ $12.90/unit</t>
   </si>
   <si>
@@ -387,7 +393,7 @@
     <t>[5pcs High Speed Memory Cards] 5pcs Memory … ×1 @ $20.71/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">4-in-1 USB Mini SD Card Reader - Compact, Effi… ×10 @ $1.60/unit
+    <t>4-in-1 USB Mini SD Card Reader - Compact, Effi… ×10 @ $1.60/unit
 USB 2.0 Type-C Flash Drive 256MB/100GB/116G… ×5 @ $5.60/unit</t>
   </si>
   <si>
@@ -397,15 +403,15 @@
     <t>TG192 Large Capacity Outdoor Wireless Speaker… ×1 @ $3.80/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">ACER TWS Wireless Earbuds with Deep Bass &amp; … ×1 @ $9.22/unit
+    <t>ACER TWS Wireless Earbuds with Deep Bass &amp; … ×1 @ $9.22/unit
 ACER TWS Wireless Earbuds with Deep Bass &amp; … ×1 @ $7.04/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">TG537 Portable Wireless Loud Speaker - TWS Sy… ×1 @ $14.46/unit
+    <t>TG537 Portable Wireless Loud Speaker - TWS Sy… ×1 @ $14.46/unit
 TG537 Portable Wireless Loud Speaker - TWS Sy… ×1 @ $12.17/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Custom Black Metal Pens, Bulk Pack, Engravable … ×1 @ $18.78/unit
+    <t>Custom Black Metal Pens, Bulk Pack, Engravable … ×1 @ $18.78/unit
 Personalized Ballpoint Pens with Laser Engravin… ×1 @ $13.26/unit
 Acer New Wireless Earbuds, Mini In-Ear Headph… ×1 @ $10.87/unit
 Acer Ohr544 In-Ear Wireless Headphones, Stere… ×1 @ $10.48/unit</t>
@@ -417,11 +423,11 @@
     <t>Nokia Go Earbuds+ TWS-201 ×2 @ $9.10/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">TG667 Is a Compact And Portable Wireless Spea… ×1 @ $10.44/unit
+    <t>TG667 Is a Compact And Portable Wireless Spea… ×1 @ $10.44/unit
 TG537 Portable Wireless Speaker - TWS Technol… ×1 @ $11.31/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Wireless Earbuds, Wireless 5.4 Bass Stereo Head… ×1 @ $9.91/unit
+    <t>Wireless Earbuds, Wireless 5.4 Bass Stereo Head… ×1 @ $9.91/unit
 Wireless Earbuds, Wireless 5.4 Bass Stereo Head… ×1 @ $14.17/unit
 [Acer] 2025 new model back-to-school season T… ×2 @ $12.73/unit
 [Acer] 2025 new model back-to-school season T… ×2 @ $10.17/unit
@@ -437,7 +443,7 @@
     <t>Shenzhen Boln Electronic Technology Co., Ltd.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hight Quality Type-c Charger Adapter T4510 45W PD Adapter US EU Plug Super Fast Charger for Samsung S24 S23 S22 Ultra S21 S20 ×40 @ $2.30/unit
+    <t>Hight Quality Type-c Charger Adapter T4510 45W PD Adapter US EU Plug Super Fast Charger for Samsung S24 S23 S22 Ultra S21 S20 ×40 @ $2.30/unit
 Airpods pro ×10 @ $5.35/unit</t>
   </si>
   <si>
@@ -462,13 +468,13 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">La Vanille 3-Piece Angel Cake Body Mist Set ×3 @ $14.99/unit
+    <t>La Vanille 3-Piece Angel Cake Body Mist Set ×3 @ $14.99/unit
 Wildflower Collection 3-Piece Morning Dew Body Mist Set | default $14.99 3 $44.97 ×3 @ $14.99/unit
 The Beaches Collection 3-Piece Let's Get Away Body Mist Set ×3 @ $14.99/unit
 The Dulce Collection 3-Piece Utopia Body Mist Set - #SQ1135328 ×3 @ $14.99/unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Men’s Salvang 3.4oz Eau De Parfume - Fathers Day Gifts ×2 @ $14.99/unit
+    <t>Men’s Salvang 3.4oz Eau De Parfume - Fathers Day Gifts ×2 @ $14.99/unit
 Mens Cologne BROSS 3.4oz Eau De Parfum Spray, Masculine Mist ×2 @ $11.99/unit
 Men’s Extreme 3.4oz Eau De Parfum - Men Perfume Spray ×2 @ $13.99/unit
 LoveryBlack Affinity For Him Pheromone Cologne – 50ml Cologn ×2 @ $21.99/unit
@@ -479,7 +485,7 @@
     <t>2026-03-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Imperial Oud (M) Eau de Parfum 100 ml Spray | ×2 @ $14.99/unit
+    <t>Imperial Oud (M) Eau de Parfum 100 ml Spray | ×2 @ $14.99/unit
 Eau de Vivre (M) Eau de Parfum 100 ml Spray | ×2 @ $14.99/unit
 Legende Intense (M) Eau de Parfum 100 ml Spray | ×2 @ $14.99/unit
 Blue Intense (M) Eau de Parfum 100 ml Spray | ×2 @ $14.99/unit
@@ -515,7 +521,7 @@
     <t>2026-04-25</t>
   </si>
   <si>
-    <t xml:space="preserve">St. Ives Soothing Body Wash for Women, Oatmeal &amp; Shea Butter, 22 fl oz ×3 @ $4.97/unit
+    <t>St. Ives Soothing Body Wash for Women, Oatmeal &amp; Shea Butter, 22 fl oz ×3 @ $4.97/unit
 Revlon ColorSilk Permanent Hair Color, Bond Repair Complex, 10 Black, 1 pack ×3 @ $4.97/unit
 Revlon ColorSilk Permanent Hair Color, Bond Repair Complex, 05 Ultra Light Ash Blonde, 1 pack ×3 @ $4.97/unit
 Revlon ColorSilk Permanent Hair Color, Bond Repair Complex, 45 Bright Auburn, 1 pack ×3 @ $4.97/unit
@@ -539,42 +545,42 @@
     <t>Equipment</t>
   </si>
   <si>
-    <t xml:space="preserve">MUNBYN Bluetooth Thermal Receipt Printer P047 (80mm POS) ×1 @ $143.99
+    <t>MUNBYN Bluetooth Thermal Receipt Printer P047 (80mm POS) ×1 @ $143.99
 MUNBYN Bluetooth Thermal Label Printer 130B (4x6 Wireless) ×1 @ $79.99</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFD4AF37"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFD4AF37"/>
       <sz val="11"/>
+      <color rgb="FFCC0000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFCC0000"/>
       <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FF111111"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1024,20 +1030,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K84"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J84"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
     <col min="5" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="60.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="60.7265625" customWidth="1"/>
+    <col min="10" max="10" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.95" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1069,7 +1075,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1101,7 +1107,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1133,7 +1139,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -1144,7 +1150,7 @@
         <v>12</v>
       </c>
       <c r="D4" s="3">
-        <v>129.08</v>
+        <v>129.08000000000001</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>13</v>
@@ -1165,7 +1171,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -1197,7 +1203,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
@@ -1229,7 +1235,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
@@ -1261,7 +1267,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -1293,7 +1299,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>30</v>
       </c>
@@ -1325,7 +1331,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>33</v>
       </c>
@@ -1357,7 +1363,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1389,7 +1395,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>38</v>
       </c>
@@ -1415,7 +1421,7 @@
         <v>123.86</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>40</v>
       </c>
@@ -1447,7 +1453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>43</v>
       </c>
@@ -1479,7 +1485,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>45</v>
       </c>
@@ -1505,7 +1511,7 @@
         <v>47.07</v>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>47</v>
       </c>
@@ -1537,7 +1543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>47</v>
       </c>
@@ -1548,7 +1554,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="10">
-        <v>162.36</v>
+        <v>162.36000000000001</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>13</v>
@@ -1563,7 +1569,7 @@
         <v>173.72</v>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
@@ -1595,7 +1601,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>51</v>
       </c>
@@ -1627,7 +1633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -1647,7 +1653,7 @@
         <v>0.99</v>
       </c>
       <c r="G20" s="3">
-        <v>32.62</v>
+        <v>32.619999999999997</v>
       </c>
       <c r="H20" s="3">
         <v>15.07</v>
@@ -1659,7 +1665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>51</v>
       </c>
@@ -1676,7 +1682,7 @@
         <v>13</v>
       </c>
       <c r="F21" s="3">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="G21" s="3">
         <v>32.46</v>
@@ -1691,7 +1697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>56</v>
       </c>
@@ -1702,7 +1708,7 @@
         <v>12</v>
       </c>
       <c r="D22" s="3">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>13</v>
@@ -1723,7 +1729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>58</v>
       </c>
@@ -1755,7 +1761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>58</v>
       </c>
@@ -1787,7 +1793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>58</v>
       </c>
@@ -1804,7 +1810,7 @@
         <v>13</v>
       </c>
       <c r="F25" s="3">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="G25" s="3">
         <v>72.42</v>
@@ -1819,7 +1825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>58</v>
       </c>
@@ -1836,7 +1842,7 @@
         <v>13</v>
       </c>
       <c r="F26" s="3">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="G26" s="3">
         <v>80.52</v>
@@ -1851,7 +1857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>63</v>
       </c>
@@ -1874,7 +1880,7 @@
         <v>11.91</v>
       </c>
       <c r="H27" s="3">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>64</v>
@@ -1883,7 +1889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>65</v>
       </c>
@@ -1906,7 +1912,7 @@
         <v>11.91</v>
       </c>
       <c r="H28" s="3">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>66</v>
@@ -1915,7 +1921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>67</v>
       </c>
@@ -1947,7 +1953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>69</v>
       </c>
@@ -1979,7 +1985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>51</v>
       </c>
@@ -2011,7 +2017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>69</v>
       </c>
@@ -2022,7 +2028,7 @@
         <v>12</v>
       </c>
       <c r="D32" s="3">
-        <v>32.2</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>13</v>
@@ -2031,10 +2037,10 @@
         <v>2.25</v>
       </c>
       <c r="G32" s="3">
-        <v>287.4</v>
+        <v>287.39999999999998</v>
       </c>
       <c r="H32" s="3">
-        <v>34.45</v>
+        <v>34.450000000000003</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>72</v>
@@ -2043,7 +2049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>69</v>
       </c>
@@ -2075,7 +2081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>69</v>
       </c>
@@ -2107,7 +2113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>69</v>
       </c>
@@ -2124,7 +2130,7 @@
         <v>13</v>
       </c>
       <c r="F35" s="3">
-        <v>2.05</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="G35" s="3">
         <v>225.6</v>
@@ -2139,7 +2145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>69</v>
       </c>
@@ -2171,7 +2177,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>69</v>
       </c>
@@ -2182,7 +2188,7 @@
         <v>12</v>
       </c>
       <c r="D37" s="3">
-        <v>140.11</v>
+        <v>140.11000000000001</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>13</v>
@@ -2203,7 +2209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>69</v>
       </c>
@@ -2235,7 +2241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>69</v>
       </c>
@@ -2258,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="3">
-        <v>34.7</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>79</v>
@@ -2267,7 +2273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>47</v>
       </c>
@@ -2299,7 +2305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>47</v>
       </c>
@@ -2331,7 +2337,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>51</v>
       </c>
@@ -2363,7 +2369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>47</v>
       </c>
@@ -2395,7 +2401,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
@@ -2427,7 +2433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>47</v>
       </c>
@@ -2459,7 +2465,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>86</v>
       </c>
@@ -2491,7 +2497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>86</v>
       </c>
@@ -2523,7 +2529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>86</v>
       </c>
@@ -2555,7 +2561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>86</v>
       </c>
@@ -2587,7 +2593,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>43</v>
       </c>
@@ -2610,7 +2616,7 @@
         <v>35.46</v>
       </c>
       <c r="H50" s="3">
-        <v>20.24</v>
+        <v>20.239999999999998</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>91</v>
@@ -2619,7 +2625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>15</v>
       </c>
@@ -2636,7 +2642,7 @@
         <v>13</v>
       </c>
       <c r="F51" s="3">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="G51" s="3">
         <v>23.56</v>
@@ -2651,7 +2657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>15</v>
       </c>
@@ -2668,7 +2674,7 @@
         <v>13</v>
       </c>
       <c r="F52" s="3">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="G52" s="3">
         <v>17</v>
@@ -2683,7 +2689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>51</v>
       </c>
@@ -2715,7 +2721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>15</v>
       </c>
@@ -2732,7 +2738,7 @@
         <v>13</v>
       </c>
       <c r="F54" s="3">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="G54" s="3">
         <v>17.12</v>
@@ -2747,7 +2753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>15</v>
       </c>
@@ -2779,7 +2785,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>15</v>
       </c>
@@ -2811,7 +2817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>15</v>
       </c>
@@ -2843,7 +2849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>15</v>
       </c>
@@ -2875,7 +2881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>15</v>
       </c>
@@ -2895,7 +2901,7 @@
         <v>3.02</v>
       </c>
       <c r="G59" s="3">
-        <v>138.95</v>
+        <v>138.94999999999999</v>
       </c>
       <c r="H59" s="3">
         <v>46.22</v>
@@ -2907,7 +2913,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>102</v>
       </c>
@@ -2939,7 +2945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>102</v>
       </c>
@@ -2950,7 +2956,7 @@
         <v>12</v>
       </c>
       <c r="D61" s="3">
-        <v>16.26</v>
+        <v>16.260000000000002</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>13</v>
@@ -2971,7 +2977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>102</v>
       </c>
@@ -2988,7 +2994,7 @@
         <v>13</v>
       </c>
       <c r="F62" s="3">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="G62" s="3">
         <v>97.41</v>
@@ -3003,7 +3009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>102</v>
       </c>
@@ -3035,7 +3041,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>51</v>
       </c>
@@ -3052,7 +3058,7 @@
         <v>13</v>
       </c>
       <c r="F64" s="3">
-        <v>0.56</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="G64" s="3">
         <v>0.82</v>
@@ -3067,7 +3073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>51</v>
       </c>
@@ -3099,7 +3105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>51</v>
       </c>
@@ -3131,7 +3137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>51</v>
       </c>
@@ -3163,7 +3169,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>51</v>
       </c>
@@ -3174,7 +3180,7 @@
         <v>12</v>
       </c>
       <c r="D68" s="3">
-        <v>9.2</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>13</v>
@@ -3195,7 +3201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>86</v>
       </c>
@@ -3212,7 +3218,7 @@
         <v>13</v>
       </c>
       <c r="F69" s="3">
-        <v>16.24</v>
+        <v>16.239999999999998</v>
       </c>
       <c r="G69" s="3">
         <v>0</v>
@@ -3227,7 +3233,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>114</v>
       </c>
@@ -3244,7 +3250,7 @@
         <v>13</v>
       </c>
       <c r="F70" s="3">
-        <v>8.96</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="G70" s="3">
         <v>0</v>
@@ -3259,7 +3265,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>13</v>
       </c>
@@ -3285,7 +3291,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>13</v>
       </c>
@@ -3311,7 +3317,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>119</v>
       </c>
@@ -3343,7 +3349,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>119</v>
       </c>
@@ -3375,7 +3381,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>123</v>
       </c>
@@ -3407,7 +3413,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="9" t="s">
         <v>123</v>
       </c>
@@ -3433,7 +3439,7 @@
         <v>459.37</v>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="9" t="s">
         <v>125</v>
       </c>
@@ -3465,7 +3471,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9" t="s">
         <v>127</v>
       </c>
@@ -3497,7 +3503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="9" t="s">
         <v>127</v>
       </c>
@@ -3529,7 +3535,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="9" t="s">
         <v>130</v>
       </c>
@@ -3561,7 +3567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="9" t="s">
         <v>130</v>
       </c>
@@ -3572,7 +3578,7 @@
         <v>12</v>
       </c>
       <c r="D81" s="10">
-        <v>35.88</v>
+        <v>35.880000000000003</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>13</v>
@@ -3593,7 +3599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
         <v>133</v>
       </c>
@@ -3625,7 +3631,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" ht="42" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="12">
         <v>46150</v>
       </c>
@@ -3657,7 +3663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="17" t="s">
         <v>7</v>
       </c>
@@ -3668,7 +3674,7 @@
         <v>13</v>
       </c>
       <c r="D84" s="17">
-        <v>4983.65</v>
+        <v>4983.6499999999996</v>
       </c>
       <c r="E84" s="17" t="s">
         <v>13</v>
@@ -3685,6 +3691,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>